--- a/SHB01D.xlsx
+++ b/SHB01D.xlsx
@@ -202,40 +202,40 @@
     <t>IDM KACANG BALI 150G</t>
   </si>
   <si>
+    <t>20135346</t>
+  </si>
+  <si>
+    <t>LRSST STK GNDM COK75</t>
+  </si>
+  <si>
+    <t>20135347</t>
+  </si>
+  <si>
+    <t>LRSST STK GNDM VNL75</t>
+  </si>
+  <si>
+    <t>20134368</t>
+  </si>
+  <si>
+    <t>IDM TLR GBUS WJEN 70</t>
+  </si>
+  <si>
+    <t>20134367</t>
+  </si>
+  <si>
+    <t>IDM TLR GBUS KEJU 70</t>
+  </si>
+  <si>
+    <t>20133192</t>
+  </si>
+  <si>
+    <t>ROCHO WFR CKLT KCG84</t>
+  </si>
+  <si>
     <t>20133790</t>
   </si>
   <si>
     <t>LRSST PPCRN CHOBRY75</t>
-  </si>
-  <si>
-    <t>20135346</t>
-  </si>
-  <si>
-    <t>LRSST STK GNDM COK75</t>
-  </si>
-  <si>
-    <t>20135347</t>
-  </si>
-  <si>
-    <t>LRSST STK GNDM VNL75</t>
-  </si>
-  <si>
-    <t>20134368</t>
-  </si>
-  <si>
-    <t>IDM TLR GBUS WJEN 70</t>
-  </si>
-  <si>
-    <t>20134367</t>
-  </si>
-  <si>
-    <t>IDM TLR GBUS KEJU 70</t>
-  </si>
-  <si>
-    <t>20133192</t>
-  </si>
-  <si>
-    <t>ROCHO WFR CKLT KCG84</t>
   </si>
   <si>
     <t>20134686</t>
@@ -1112,7 +1112,7 @@
         <v>30</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>25</v>
@@ -1132,7 +1132,7 @@
         <v>30</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -1152,7 +1152,7 @@
         <v>30</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -1172,7 +1172,7 @@
         <v>30</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>25</v>
@@ -1192,7 +1192,7 @@
         <v>30</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>25</v>
@@ -1212,7 +1212,7 @@
         <v>30</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>25</v>
@@ -1229,10 +1229,10 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -1252,7 +1252,7 @@
         <v>14</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -1272,7 +1272,7 @@
         <v>14</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -1292,7 +1292,7 @@
         <v>14</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -1312,7 +1312,7 @@
         <v>14</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>5</v>
@@ -1332,10 +1332,10 @@
         <v>14</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1352,10 +1352,10 @@
         <v>14</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">

--- a/SHB01D.xlsx
+++ b/SHB01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="97">
   <si>
     <t/>
   </si>
@@ -236,6 +236,12 @@
   </si>
   <si>
     <t>LRSST PPCRN CHOBRY75</t>
+  </si>
+  <si>
+    <t>20142232</t>
+  </si>
+  <si>
+    <t>IDM POPCRN CHOCO 65G</t>
   </si>
   <si>
     <t>20134686</t>
@@ -688,7 +694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1369,13 +1375,13 @@
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1392,10 +1398,10 @@
         <v>17</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1412,10 +1418,10 @@
         <v>17</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1432,7 +1438,7 @@
         <v>17</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -1452,7 +1458,7 @@
         <v>17</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -1472,7 +1478,7 @@
         <v>17</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -1492,7 +1498,7 @@
         <v>17</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -1512,18 +1518,18 @@
         <v>17</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -1532,9 +1538,29 @@
         <v>17</v>
       </c>
       <c r="E42" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="B43" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>25</v>
       </c>
     </row>

--- a/SHB01D.xlsx
+++ b/SHB01D.xlsx
@@ -163,7 +163,7 @@
     <t>20072370</t>
   </si>
   <si>
-    <t>IDM KCNG BUMBU 150G</t>
+    <t>IDM KCNG BUMBU 100G</t>
   </si>
   <si>
     <t>20072230</t>

--- a/SHB01D.xlsx
+++ b/SHB01D.xlsx
@@ -127,13 +127,13 @@
     <t>20096677</t>
   </si>
   <si>
-    <t>IDM SOES COKELAT 80</t>
+    <t>IDM SOES CKLT 80 G</t>
   </si>
   <si>
     <t>20136102</t>
   </si>
   <si>
-    <t>IDM SOES STROBERI80G</t>
+    <t>IDM SOES STRW 80 G</t>
   </si>
   <si>
     <t>20088416</t>
@@ -241,7 +241,7 @@
     <t>20142232</t>
   </si>
   <si>
-    <t>IDM POPCRN CHOCO 65G</t>
+    <t>IDM POPCRN CHOC 65 G</t>
   </si>
   <si>
     <t>20134686</t>
@@ -289,7 +289,7 @@
     <t>20097515</t>
   </si>
   <si>
-    <t>IDM POP CORN CRML 75</t>
+    <t>IDM POPCRN CRML 75 G</t>
   </si>
   <si>
     <t>8</t>
@@ -298,7 +298,7 @@
     <t>20102071</t>
   </si>
   <si>
-    <t>IDM POPCRN SW.CHS 65</t>
+    <t>IDM POPCRN S.CH 65 G</t>
   </si>
   <si>
     <t>9</t>

--- a/SHB01D.xlsx
+++ b/SHB01D.xlsx
@@ -127,13 +127,13 @@
     <t>20096677</t>
   </si>
   <si>
-    <t>IDM SOES CKLT 80 G</t>
+    <t>IDM SOES COKELAT 80</t>
   </si>
   <si>
     <t>20136102</t>
   </si>
   <si>
-    <t>IDM SOES STRW 80 G</t>
+    <t>IDM SOES STROBERI80G</t>
   </si>
   <si>
     <t>20088416</t>
@@ -241,7 +241,7 @@
     <t>20142232</t>
   </si>
   <si>
-    <t>IDM POPCRN CHOC 65 G</t>
+    <t>IDM POPCRN CHOCO 65G</t>
   </si>
   <si>
     <t>20134686</t>
@@ -289,7 +289,7 @@
     <t>20097515</t>
   </si>
   <si>
-    <t>IDM POPCRN CRML 75 G</t>
+    <t>IDM POP CORN CRML 75</t>
   </si>
   <si>
     <t>8</t>
@@ -298,7 +298,7 @@
     <t>20102071</t>
   </si>
   <si>
-    <t>IDM POPCRN S.CH 65 G</t>
+    <t>IDM POPCRN SW.CHS 65</t>
   </si>
   <si>
     <t>9</t>

--- a/SHB01D.xlsx
+++ b/SHB01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="95">
   <si>
     <t/>
   </si>
@@ -248,12 +248,6 @@
   </si>
   <si>
     <t>IDM KCG PISTACHIO 55</t>
-  </si>
-  <si>
-    <t>20133914</t>
-  </si>
-  <si>
-    <t>IDM CHKPEAS JG.BKR60</t>
   </si>
   <si>
     <t>20128291</t>
@@ -694,7 +688,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1418,10 +1412,10 @@
         <v>17</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1438,7 +1432,7 @@
         <v>17</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -1458,7 +1452,7 @@
         <v>17</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -1478,7 +1472,7 @@
         <v>17</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -1498,7 +1492,7 @@
         <v>17</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -1518,18 +1512,18 @@
         <v>17</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -1538,29 +1532,9 @@
         <v>17</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F43" s="1" t="s">
         <v>25</v>
       </c>
     </row>

--- a/SHB01D.xlsx
+++ b/SHB01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="93">
   <si>
     <t/>
   </si>
@@ -152,12 +152,6 @@
   </si>
   <si>
     <t>IDM KACANG KRIUK 95G</t>
-  </si>
-  <si>
-    <t>20135618</t>
-  </si>
-  <si>
-    <t>LRSST FRNCH ORIGNL65</t>
   </si>
   <si>
     <t>20072370</t>
@@ -688,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1089,13 +1083,13 @@
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1112,10 +1106,10 @@
         <v>30</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1132,7 +1126,7 @@
         <v>30</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -1152,10 +1146,10 @@
         <v>30</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1172,7 +1166,7 @@
         <v>30</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>25</v>
@@ -1192,7 +1186,7 @@
         <v>30</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>25</v>
@@ -1212,10 +1206,10 @@
         <v>30</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1229,10 +1223,10 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -1252,7 +1246,7 @@
         <v>14</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -1272,7 +1266,7 @@
         <v>14</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -1292,7 +1286,7 @@
         <v>14</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -1312,10 +1306,10 @@
         <v>14</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1332,10 +1326,10 @@
         <v>14</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1352,10 +1346,10 @@
         <v>14</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1369,13 +1363,13 @@
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1392,7 +1386,7 @@
         <v>17</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -1412,7 +1406,7 @@
         <v>17</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -1432,7 +1426,7 @@
         <v>17</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -1452,7 +1446,7 @@
         <v>17</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -1472,7 +1466,7 @@
         <v>17</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -1492,18 +1486,18 @@
         <v>17</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -1512,29 +1506,9 @@
         <v>17</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F42" s="1" t="s">
         <v>25</v>
       </c>
     </row>

--- a/SHB01D.xlsx
+++ b/SHB01D.xlsx
@@ -193,7 +193,7 @@
     <t>20047037</t>
   </si>
   <si>
-    <t>IDM KACANG BALI 150G</t>
+    <t>IDM KCANG BALI 150 G</t>
   </si>
   <si>
     <t>20135346</t>

--- a/SHB01D.xlsx
+++ b/SHB01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="96">
   <si>
     <t/>
   </si>
@@ -290,6 +290,15 @@
   </si>
   <si>
     <t>9</t>
+  </si>
+  <si>
+    <t>20143939</t>
+  </si>
+  <si>
+    <t>IDM KCANG METE ORI65</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
 </sst>
 </file>
@@ -682,13 +691,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="5" width="3" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1512,6 +1522,26 @@
         <v>25</v>
       </c>
     </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
